--- a/docs/Rough_kW_kVA_Table.xlsx
+++ b/docs/Rough_kW_kVA_Table.xlsx
@@ -10,6 +10,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" name="BREAKER_RATING_A" vbProcedure="false">Sheet1!$B$14</definedName>
+    <definedName function="false" hidden="false" name="CONTINUOUS_DUTY_DERATE" vbProcedure="false">Sheet1!$B$15</definedName>
+    <definedName function="false" hidden="false" name="ev_apparent_power_kva" vbProcedure="false">Sheet1!$B$18</definedName>
+    <definedName function="false" hidden="false" name="ev_pilot_current_a" vbProcedure="false">Sheet1!$B$17</definedName>
+    <definedName function="false" hidden="false" name="ev_real_power_kw" vbProcedure="false">Sheet1!$B$19</definedName>
+    <definedName function="false" hidden="false" name="EV_TRUE_POWER_FACTOR" vbProcedure="false">Sheet1!$B$16</definedName>
+    <definedName function="false" hidden="false" name="PANEL_VOLTAGE_V" vbProcedure="false">Sheet1!$B$13</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -20,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t xml:space="preserve">kW</t>
   </si>
@@ -29,6 +38,27 @@
   </si>
   <si>
     <t xml:space="preserve">PF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANEL_VOLTAGE_V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREAKER_RATING_A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTINUOUS_DUTY_DERATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV_TRUE_POWER_FACTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ev_pilot_current_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ev_apparent_power_kva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ev_real_power_kw</t>
   </si>
 </sst>
 </file>
@@ -44,6 +74,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -103,12 +134,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -129,9 +164,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.39"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.52"/>
   </cols>
   <sheetData>
@@ -144,13 +180,13 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="2" t="n">
         <v>6.666</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="n">
@@ -163,13 +199,14 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="2" t="n">
+        <f aca="false">B16</f>
         <v>0.99</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="n">
@@ -182,7 +219,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="n">
@@ -195,7 +232,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="n">
@@ -208,7 +245,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="n">
@@ -221,7 +258,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="n">
@@ -234,7 +271,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="n">
@@ -247,7 +284,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="n">
@@ -260,7 +297,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="D10" s="1" t="n">
@@ -273,7 +310,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="D11" s="1" t="n">
@@ -283,6 +320,65 @@
       <c r="E11" s="1" t="n">
         <f aca="false">D11/$B$3</f>
         <v>67.3333333333333</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <f aca="false"> BREAKER_RATING_A * CONTINUOUS_DUTY_DERATE</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <f aca="false"> PANEL_VOLTAGE_V * ev_pilot_current_a / 1000</f>
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <f aca="false"> ev_apparent_power_kva * EV_TRUE_POWER_FACTOR</f>
+        <v>6.58944</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Rough_kW_kVA_Table.xlsx
+++ b/docs/Rough_kW_kVA_Table.xlsx
@@ -11,13 +11,13 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="BREAKER_RATING_A" vbProcedure="false">Sheet1!$B$14</definedName>
-    <definedName function="false" hidden="false" name="CONTINUOUS_DUTY_DERATE" vbProcedure="false">Sheet1!$B$15</definedName>
-    <definedName function="false" hidden="false" name="ev_apparent_power_kva" vbProcedure="false">Sheet1!$B$18</definedName>
-    <definedName function="false" hidden="false" name="ev_pilot_current_a" vbProcedure="false">Sheet1!$B$17</definedName>
-    <definedName function="false" hidden="false" name="ev_real_power_kw" vbProcedure="false">Sheet1!$B$19</definedName>
-    <definedName function="false" hidden="false" name="EV_TRUE_POWER_FACTOR" vbProcedure="false">Sheet1!$B$16</definedName>
-    <definedName function="false" hidden="false" name="PANEL_VOLTAGE_V" vbProcedure="false">Sheet1!$B$13</definedName>
+    <definedName function="false" hidden="false" name="BREAKER_RATING_A" vbProcedure="false">Sheet1!$B$17</definedName>
+    <definedName function="false" hidden="false" name="CONTINUOUS_DUTY_DERATE" vbProcedure="false">Sheet1!$B$18</definedName>
+    <definedName function="false" hidden="false" name="ev_apparent_power_kva" vbProcedure="false">Sheet1!$B$21</definedName>
+    <definedName function="false" hidden="false" name="ev_pilot_current_a" vbProcedure="false">Sheet1!$B$20</definedName>
+    <definedName function="false" hidden="false" name="ev_real_power_kw" vbProcedure="false">Sheet1!$B$22</definedName>
+    <definedName function="false" hidden="false" name="EV_TRUE_POWER_FACTOR" vbProcedure="false">Sheet1!$B$19</definedName>
+    <definedName function="false" hidden="false" name="PANEL_VOLTAGE_V" vbProcedure="false">Sheet1!$B$16</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -29,7 +29,34 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+  <si>
+    <t xml:space="preserve">ROUGH KW AND KVA APPROXIMATIONS VS. EXACT NUMBERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rough values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exact values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rough minus Exact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. of EVs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total kVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per EV kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per EV kVA</t>
+  </si>
   <si>
     <t xml:space="preserve">kW</t>
   </si>
@@ -69,7 +96,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -91,6 +118,19 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -100,12 +140,19 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -134,12 +181,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -164,220 +223,693 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:R22"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.39"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="1.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="1" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="1.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="1" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="1.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="1" width="9.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="E3" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>6.666</v>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="P3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>6.666</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <f aca="false">$B$2 *C2</f>
-        <v>6.666</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <f aca="false">D2/$B$3</f>
-        <v>6.73333333333333</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="D5" s="5"/>
+      <c r="E5" s="1" t="n">
+        <f aca="false">$B$5 *C5</f>
+        <v>6.666</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <f aca="false">E5/$B$6</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <f aca="false">E5/$C5</f>
+        <v>6.666</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <f aca="false">F5/$C5</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" s="1" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <f aca="false">J5/$C5</f>
+        <v>6.95</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <f aca="false">K5/$C5</f>
+        <v>7.37</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <f aca="false">J5 / K5</f>
+        <v>0.943012211668928</v>
+      </c>
+      <c r="O5" s="5"/>
+      <c r="P5" s="1" t="n">
+        <f aca="false">G5 - L5</f>
+        <v>-0.284</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <f aca="false">H5 - M5</f>
+        <v>-0.567959183673469</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <f aca="false">$B$6 - N5</f>
+        <v>0.0369877883310719</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <f aca="false">B16</f>
-        <v>0.99</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <f aca="false">$B$2 *C3</f>
+      <c r="D6" s="5"/>
+      <c r="E6" s="1" t="n">
+        <f aca="false">$B$5 *C6</f>
         <v>13.332</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <f aca="false">D3/$B$3</f>
-        <v>13.4666666666667</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="2" t="n">
+      <c r="F6" s="1" t="n">
+        <f aca="false">E6/$B$6</f>
+        <v>13.6040816326531</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <f aca="false">E6/$C6</f>
+        <v>6.666</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <f aca="false">F6/$C6</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="1" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <f aca="false">J6/$C6</f>
+        <v>6.79</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <f aca="false">K6/$C6</f>
+        <v>7.005</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <f aca="false">J6 / K6</f>
+        <v>0.969307637401856</v>
+      </c>
+      <c r="O6" s="5"/>
+      <c r="P6" s="1" t="n">
+        <f aca="false">G6 - L6</f>
+        <v>-0.124</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <f aca="false">H6 - M6</f>
+        <v>-0.202959183673469</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <f aca="false">$B$6 - N6</f>
+        <v>0.0106923625981441</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <f aca="false">$B$2 *C4</f>
+      <c r="D7" s="5"/>
+      <c r="E7" s="1" t="n">
+        <f aca="false">$B$5 *C7</f>
         <v>19.998</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <f aca="false">D4/$B$3</f>
-        <v>20.2</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="2" t="n">
+      <c r="F7" s="1" t="n">
+        <f aca="false">E7/$B$6</f>
+        <v>20.4061224489796</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <f aca="false">E7/$C7</f>
+        <v>6.666</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <f aca="false">F7/$C7</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="1" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <f aca="false">J7/$C7</f>
+        <v>6.74333333333333</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <f aca="false">K7/$C7</f>
+        <v>6.90666666666667</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <f aca="false">J7 / K7</f>
+        <v>0.976351351351351</v>
+      </c>
+      <c r="O7" s="5"/>
+      <c r="P7" s="1" t="n">
+        <f aca="false">G7 - L7</f>
+        <v>-0.0773333333333328</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <f aca="false">H7 - M7</f>
+        <v>-0.104625850340135</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <f aca="false">$B$6 - N7</f>
+        <v>0.00364864864864856</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <f aca="false">$B$2 *C5</f>
+      <c r="D8" s="5"/>
+      <c r="E8" s="1" t="n">
+        <f aca="false">$B$5 *C8</f>
         <v>26.664</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <f aca="false">D5/$B$3</f>
-        <v>26.9333333333333</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="2" t="n">
+      <c r="F8" s="1" t="n">
+        <f aca="false">E8/$B$6</f>
+        <v>27.2081632653061</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <f aca="false">E8/$C8</f>
+        <v>6.666</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <f aca="false">F8/$C8</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="1" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <f aca="false">J8/$C8</f>
+        <v>6.7275</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <f aca="false">K8/$C8</f>
+        <v>6.87</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <f aca="false">J8 / K8</f>
+        <v>0.979257641921397</v>
+      </c>
+      <c r="O8" s="5"/>
+      <c r="P8" s="1" t="n">
+        <f aca="false">G8 - L8</f>
+        <v>-0.0614999999999997</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <f aca="false">H8 - M8</f>
+        <v>-0.0679591836734694</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <f aca="false">$B$6 - N8</f>
+        <v>0.000742358078602567</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <f aca="false">$B$2 *C6</f>
+      <c r="D9" s="5"/>
+      <c r="E9" s="1" t="n">
+        <f aca="false">$B$5 *C9</f>
         <v>33.33</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <f aca="false">D6/$B$3</f>
-        <v>33.6666666666667</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="2" t="n">
+      <c r="F9" s="1" t="n">
+        <f aca="false">E9/$B$6</f>
+        <v>34.0102040816326</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <f aca="false">E9/$C9</f>
+        <v>6.666</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <f aca="false">F9/$C9</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="1" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <f aca="false">J9/$C9</f>
+        <v>6.722</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <f aca="false">K9/$C9</f>
+        <v>6.856</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <f aca="false">J9 / K9</f>
+        <v>0.980455075845974</v>
+      </c>
+      <c r="O9" s="5"/>
+      <c r="P9" s="1" t="n">
+        <f aca="false">G9 - L9</f>
+        <v>-0.0560000000000001</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <f aca="false">H9 - M9</f>
+        <v>-0.0539591836734701</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <f aca="false">$B$6 - N9</f>
+        <v>-0.000455075845974262</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <f aca="false">$B$2 *C7</f>
+      <c r="D10" s="5"/>
+      <c r="E10" s="1" t="n">
+        <f aca="false">$B$5 *C10</f>
         <v>39.996</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <f aca="false">D7/$B$3</f>
-        <v>40.4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="2" t="n">
+      <c r="F10" s="1" t="n">
+        <f aca="false">E10/$B$6</f>
+        <v>40.8122448979592</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <f aca="false">E10/$C10</f>
+        <v>6.666</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <f aca="false">F10/$C10</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="1" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <f aca="false">J10/$C10</f>
+        <v>6.72333333333333</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <f aca="false">K10/$C10</f>
+        <v>6.85166666666667</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <f aca="false">J10 / K10</f>
+        <v>0.981269764047677</v>
+      </c>
+      <c r="O10" s="5"/>
+      <c r="P10" s="1" t="n">
+        <f aca="false">G10 - L10</f>
+        <v>-0.0573333333333332</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <f aca="false">H10 - M10</f>
+        <v>-0.049625850340135</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <f aca="false">$B$6 - N10</f>
+        <v>-0.00126976404767709</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <f aca="false">$B$2 *C8</f>
+      <c r="D11" s="5"/>
+      <c r="E11" s="1" t="n">
+        <f aca="false">$B$5 *C11</f>
         <v>46.662</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <f aca="false">D8/$B$3</f>
-        <v>47.1333333333333</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="2" t="n">
+      <c r="F11" s="1" t="n">
+        <f aca="false">E11/$B$6</f>
+        <v>47.6142857142857</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <f aca="false">E11/$C11</f>
+        <v>6.666</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <f aca="false">F11/$C11</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="1" t="n">
+        <v>47.09</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <f aca="false">J11/$C11</f>
+        <v>6.72714285714286</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <f aca="false">K11/$C11</f>
+        <v>6.85285714285714</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <f aca="false">J11 / K11</f>
+        <v>0.981655201167396</v>
+      </c>
+      <c r="O11" s="5"/>
+      <c r="P11" s="1" t="n">
+        <f aca="false">G11 - L11</f>
+        <v>-0.0611428571428583</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <f aca="false">H11 - M11</f>
+        <v>-0.0508163265306116</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <f aca="false">$B$6 - N11</f>
+        <v>-0.00165520116739637</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <f aca="false">$B$2 *C9</f>
+      <c r="D12" s="5"/>
+      <c r="E12" s="1" t="n">
+        <f aca="false">$B$5 *C12</f>
         <v>53.328</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <f aca="false">D9/$B$3</f>
-        <v>53.8666666666667</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="2" t="n">
+      <c r="F12" s="1" t="n">
+        <f aca="false">E12/$B$6</f>
+        <v>54.4163265306123</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <f aca="false">E12/$C12</f>
+        <v>6.666</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <f aca="false">F12/$C12</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="1" t="n">
+        <v>53.87</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <f aca="false">J12/$C12</f>
+        <v>6.73375</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <f aca="false">K12/$C12</f>
+        <v>6.85875</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <f aca="false">J12 / K12</f>
+        <v>0.981775104793147</v>
+      </c>
+      <c r="O12" s="5"/>
+      <c r="P12" s="1" t="n">
+        <f aca="false">G12 - L12</f>
+        <v>-0.0677499999999993</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <f aca="false">H12 - M12</f>
+        <v>-0.056709183673469</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <f aca="false">$B$6 - N12</f>
+        <v>-0.00177510479314746</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <f aca="false">$B$2 *C10</f>
+      <c r="D13" s="5"/>
+      <c r="E13" s="1" t="n">
+        <f aca="false">$B$5 *C13</f>
         <v>59.994</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <f aca="false">D10/$B$3</f>
-        <v>60.6</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="2" t="n">
+      <c r="F13" s="1" t="n">
+        <f aca="false">E13/$B$6</f>
+        <v>61.2183673469388</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <f aca="false">E13/$C13</f>
+        <v>6.666</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <f aca="false">F13/$C13</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="1" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <f aca="false">J13/$C13</f>
+        <v>6.74222222222222</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <f aca="false">K13/$C13</f>
+        <v>6.86666666666667</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <f aca="false">J13 / K13</f>
+        <v>0.981877022653722</v>
+      </c>
+      <c r="O13" s="5"/>
+      <c r="P13" s="1" t="n">
+        <f aca="false">G13 - L13</f>
+        <v>-0.0762222222222215</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <f aca="false">H13 - M13</f>
+        <v>-0.0646258503401356</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <f aca="false">$B$6 - N13</f>
+        <v>-0.00187702265372169</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <f aca="false">$B$2 *C11</f>
+      <c r="D14" s="5"/>
+      <c r="E14" s="1" t="n">
+        <f aca="false">$B$5 *C14</f>
         <v>66.66</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <f aca="false">D11/$B$3</f>
-        <v>67.3333333333333</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="0" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="0" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="0" t="n">
-        <v>0.8</v>
+      <c r="F14" s="1" t="n">
+        <f aca="false">E14/$B$6</f>
+        <v>68.0204081632653</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <f aca="false">E14/$C14</f>
+        <v>6.666</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <f aca="false">F14/$C14</f>
+        <v>6.80204081632653</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="1" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>68.77</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <f aca="false">J14/$C14</f>
+        <v>6.75</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <f aca="false">K14/$C14</f>
+        <v>6.877</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <f aca="false">J14 / K14</f>
+        <v>0.981532645048713</v>
+      </c>
+      <c r="O14" s="5"/>
+      <c r="P14" s="1" t="n">
+        <f aca="false">G14 - L14</f>
+        <v>-0.0840000000000005</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <f aca="false">H14 - M14</f>
+        <v>-0.07495918367347</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <f aca="false">$B$6 - N14</f>
+        <v>-0.0015326450487132</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.99</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B17" s="0" t="n">
-        <f aca="false"> BREAKER_RATING_A * CONTINUOUS_DUTY_DERATE</f>
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B18" s="0" t="n">
-        <f aca="false"> PANEL_VOLTAGE_V * ev_pilot_current_a / 1000</f>
-        <v>6.656</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B19" s="0" t="n">
-        <f aca="false"> ev_apparent_power_kva * EV_TRUE_POWER_FACTOR</f>
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <f aca="false">BREAKER_RATING_A * CONTINUOUS_DUTY_DERATE</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <f aca="false">PANEL_VOLTAGE_V * ev_pilot_current_a / 1000</f>
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <f aca="false">ev_apparent_power_kva * EV_TRUE_POWER_FACTOR</f>
         <v>6.58944</v>
       </c>
     </row>
